--- a/tests/fixtures/osoby.xlsx
+++ b/tests/fixtures/osoby.xlsx
@@ -6,13 +6,14 @@
   <sheets>
     <sheet sheetId="1" name="Twórcy" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="Kamerzyści" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Pusty" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6920" uniqueCount="4569">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6922" uniqueCount="4569">
   <si>
     <t>Imię</t>
   </si>
@@ -37139,4 +37140,23 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
 </file>